--- a/data/out/variants/v7_only_gen_enso/summary_v7_only_gen_enso.xlsx
+++ b/data/out/variants/v7_only_gen_enso/summary_v7_only_gen_enso.xlsx
@@ -547,7 +547,7 @@
         <v>9639</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02698802947998047</v>
+        <v>0.03047490119934082</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         <v>9639</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02532625198364258</v>
+        <v>0.02348852157592773</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         <v>9639</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09516382217407227</v>
+        <v>0.05550599098205566</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         <v>9639</v>
       </c>
       <c r="M5" t="n">
-        <v>14.7310266494751</v>
+        <v>4.033093214035034</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>9639</v>
       </c>
       <c r="M6" t="n">
-        <v>2.871998071670532</v>
+        <v>1.312177181243896</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.1102014355671057</v>
+        <v>0.1102014355671058</v>
       </c>
       <c r="F7" t="n">
         <v>267.0974971988797</v>
       </c>
       <c r="G7" t="n">
-        <v>223599.0509299944</v>
+        <v>223599.0509299943</v>
       </c>
       <c r="H7" t="n">
-        <v>472.8626131658057</v>
+        <v>472.8626131658056</v>
       </c>
       <c r="I7" t="n">
         <v>55.97387097910575</v>
@@ -818,7 +818,7 @@
         <v>9639</v>
       </c>
       <c r="M7" t="n">
-        <v>763.820885181427</v>
+        <v>237.2343280315399</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>9639</v>
       </c>
       <c r="M8" t="n">
-        <v>398.3267982006073</v>
+        <v>160.1045513153076</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>9639</v>
       </c>
       <c r="M9" t="n">
-        <v>247.7403934001923</v>
+        <v>112.068421125412</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>9639</v>
       </c>
       <c r="M10" t="n">
-        <v>0.963275671005249</v>
+        <v>0.5615699291229248</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1018,23 +1018,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 883, 'learning_rate': 0.05781558755031934, 'max_depth': 3, 'subsample': 0.8478052658281287, 'colsample_bytree': 0.8471027133538456}</t>
+          <t>{'n_estimators': 562, 'learning_rate': 0.08893846137233828, 'max_depth': 3, 'subsample': 0.9765606472505644, 'colsample_bytree': 0.9002112877093617}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.2437167787713618</v>
+        <v>0.2468837882963378</v>
       </c>
       <c r="F11" t="n">
-        <v>242.6813571799569</v>
+        <v>239.8370078677856</v>
       </c>
       <c r="G11" t="n">
-        <v>190047.7448047802</v>
+        <v>189251.9013943986</v>
       </c>
       <c r="H11" t="n">
-        <v>435.9446579610538</v>
+        <v>435.0309200440799</v>
       </c>
       <c r="I11" t="n">
-        <v>46.78080168170353</v>
+        <v>46.14101605300032</v>
       </c>
       <c r="J11" t="n">
         <v>48192</v>
@@ -1046,7 +1046,7 @@
         <v>9639</v>
       </c>
       <c r="M11" t="n">
-        <v>84.91400790214539</v>
+        <v>41.9045090675354</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1073,23 +1073,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 292, 'learning_rate': 0.015932139742250856, 'num_leaves': 101, 'min_child_samples': 50}</t>
+          <t>{'n_estimators': 774, 'learning_rate': 0.015044230089777247, 'num_leaves': 84, 'min_child_samples': 50}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.1766973401843501</v>
+        <v>0.1629537812051705</v>
       </c>
       <c r="F12" t="n">
-        <v>249.102788498915</v>
+        <v>251.333561340796</v>
       </c>
       <c r="G12" t="n">
-        <v>206889.1777547959</v>
+        <v>210342.8209353775</v>
       </c>
       <c r="H12" t="n">
-        <v>454.8507202971057</v>
+        <v>458.6314652696406</v>
       </c>
       <c r="I12" t="n">
-        <v>49.04243301545075</v>
+        <v>49.05016943141953</v>
       </c>
       <c r="J12" t="n">
         <v>48192</v>
@@ -1101,7 +1101,7 @@
         <v>9639</v>
       </c>
       <c r="M12" t="n">
-        <v>339.1843287944794</v>
+        <v>151.8796892166138</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1128,23 +1128,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'iterations': 403, 'learning_rate': 0.08334880391209665, 'depth': 4}</t>
+          <t>{'iterations': 997, 'learning_rate': 0.09576052300830688, 'depth': 4}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.1980695194134733</v>
+        <v>0.2032725028454707</v>
       </c>
       <c r="F13" t="n">
-        <v>248.8954745114753</v>
+        <v>248.4850550113974</v>
       </c>
       <c r="G13" t="n">
-        <v>201518.5251341285</v>
+        <v>200211.0582490357</v>
       </c>
       <c r="H13" t="n">
-        <v>448.9081477698177</v>
+        <v>447.4495035744656</v>
       </c>
       <c r="I13" t="n">
-        <v>47.73272340611069</v>
+        <v>49.71428824226196</v>
       </c>
       <c r="J13" t="n">
         <v>48192</v>
@@ -1156,7 +1156,7 @@
         <v>9639</v>
       </c>
       <c r="M13" t="n">
-        <v>220.8434581756592</v>
+        <v>110.2313058376312</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>9639</v>
       </c>
       <c r="M14" t="n">
-        <v>121.8468010425568</v>
+        <v>39.85043811798096</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>9639</v>
       </c>
       <c r="M15" t="n">
-        <v>28.68540501594543</v>
+        <v>8.046984672546387</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>9639</v>
       </c>
       <c r="M16" t="n">
-        <v>1655.074973344803</v>
+        <v>780.1351373195648</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
